--- a/data/historial/2026-07-24.xlsx
+++ b/data/historial/2026-07-24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E2FE38B-CA03-477D-88BE-58C62E824954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143515A0-4BC8-444E-996F-CBCCEEE98983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2055,7 +2055,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2303,6 +2303,9 @@
     <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="18" fillId="34" borderId="25" xfId="47" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2329,10 +2332,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="138">
@@ -2819,1224 +2818,1224 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="144" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="154" t="s">
+      <c r="B1" s="144" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="154" t="s">
+      <c r="C1" s="144" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="154" t="s">
+      <c r="D1" s="144" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="154" t="s">
+      <c r="E1" s="144" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="154" t="s">
+      <c r="F1" s="144" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="154" t="s">
+      <c r="G1" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="H1" s="154" t="s">
+      <c r="H1" s="144" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="153" t="s">
+      <c r="A2" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="153">
-        <v>0</v>
-      </c>
-      <c r="C2" s="153">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>79578.740710482307</v>
       </c>
-      <c r="D2" s="153">
+      <c r="D2">
         <v>382189.7035248453</v>
       </c>
-      <c r="E2" s="153">
+      <c r="E2">
         <v>1418619879.6159928</v>
       </c>
-      <c r="F2" s="153">
-        <v>0</v>
-      </c>
-      <c r="G2" s="153">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>641418.61484977743</v>
       </c>
-      <c r="H2" s="153">
+      <c r="H2">
         <v>641418.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="153" t="s">
+      <c r="A3" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="153">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="153">
+      <c r="C3">
         <v>900.96427287259996</v>
       </c>
-      <c r="D3" s="153">
+      <c r="D3">
         <v>1582.2693988123001</v>
       </c>
-      <c r="E3" s="153">
+      <c r="E3">
         <v>21380620.494992524</v>
       </c>
-      <c r="F3" s="153">
-        <v>0</v>
-      </c>
-      <c r="G3" s="153">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>641418.61484977743</v>
       </c>
-      <c r="H3" s="153">
+      <c r="H3">
         <v>641418.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="153" t="s">
+      <c r="A4" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="153">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="153">
+      <c r="C4">
         <v>528.0071097865</v>
       </c>
-      <c r="D4" s="153">
+      <c r="D4">
         <v>1186.8255357126</v>
       </c>
-      <c r="E4" s="153">
+      <c r="E4">
         <v>13323959.077569095</v>
       </c>
-      <c r="F4" s="153">
-        <v>0</v>
-      </c>
-      <c r="G4" s="153">
-        <v>0</v>
-      </c>
-      <c r="H4" s="153">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="153" t="s">
+      <c r="A5" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="153">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="153">
+      <c r="C5">
         <v>1060.6763293618999</v>
       </c>
-      <c r="D5" s="153">
+      <c r="D5">
         <v>4508.2886190593999</v>
       </c>
-      <c r="E5" s="153">
+      <c r="E5">
         <v>23206009.330480266</v>
       </c>
-      <c r="F5" s="153">
-        <v>0</v>
-      </c>
-      <c r="G5" s="153">
-        <v>0</v>
-      </c>
-      <c r="H5" s="153">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="153" t="s">
+      <c r="A6" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="153">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="153">
+      <c r="C6">
         <v>1360.6290674586</v>
       </c>
-      <c r="D6" s="153">
+      <c r="D6">
         <v>3746.6424881104999</v>
       </c>
-      <c r="E6" s="153">
+      <c r="E6">
         <v>33030100.130732697</v>
       </c>
-      <c r="F6" s="153">
-        <v>0</v>
-      </c>
-      <c r="G6" s="153">
-        <v>0</v>
-      </c>
-      <c r="H6" s="153">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="153" t="s">
+      <c r="A7" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="153">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="153">
+      <c r="C7">
         <v>1825.2059898555999</v>
       </c>
-      <c r="D7" s="153">
+      <c r="D7">
         <v>6640.5699171246997</v>
       </c>
-      <c r="E7" s="153">
+      <c r="E7">
         <v>34506733.881239109</v>
       </c>
-      <c r="F7" s="153">
-        <v>0</v>
-      </c>
-      <c r="G7" s="153">
-        <v>0</v>
-      </c>
-      <c r="H7" s="153">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="153" t="s">
+      <c r="A8" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="153">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="153">
+      <c r="C8">
         <v>4317.7249999999003</v>
       </c>
-      <c r="D8" s="153">
+      <c r="D8">
         <v>12166.03</v>
       </c>
-      <c r="E8" s="153">
+      <c r="E8">
         <v>78964296.522824496</v>
       </c>
-      <c r="F8" s="153">
-        <v>0</v>
-      </c>
-      <c r="G8" s="153">
-        <v>0</v>
-      </c>
-      <c r="H8" s="153">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="153" t="s">
+      <c r="A9" t="s">
         <v>271</v>
       </c>
-      <c r="B9" s="153">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="153">
+      <c r="C9">
         <v>822.20710317370003</v>
       </c>
-      <c r="D9" s="153">
+      <c r="D9">
         <v>3003.6785833503</v>
       </c>
-      <c r="E9" s="153">
+      <c r="E9">
         <v>16883619.323650431</v>
       </c>
-      <c r="F9" s="153">
-        <v>0</v>
-      </c>
-      <c r="G9" s="153">
-        <v>0</v>
-      </c>
-      <c r="H9" s="153">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="153" t="s">
+      <c r="A10" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="153">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="153">
+      <c r="C10">
         <v>440.39840872939999</v>
       </c>
-      <c r="D10" s="153">
+      <c r="D10">
         <v>1823.6359405005001</v>
       </c>
-      <c r="E10" s="153">
+      <c r="E10">
         <v>13694761.317613492</v>
       </c>
-      <c r="F10" s="153">
-        <v>0</v>
-      </c>
-      <c r="G10" s="153">
-        <v>0</v>
-      </c>
-      <c r="H10" s="153">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="153" t="s">
+      <c r="A11" t="s">
         <v>210</v>
       </c>
-      <c r="B11" s="153">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="153">
+      <c r="C11">
         <v>761.97329365040002</v>
       </c>
-      <c r="D11" s="153">
+      <c r="D11">
         <v>2419.4262500145001</v>
       </c>
-      <c r="E11" s="153">
+      <c r="E11">
         <v>14082645.129487799</v>
       </c>
-      <c r="F11" s="153">
-        <v>0</v>
-      </c>
-      <c r="G11" s="153">
-        <v>0</v>
-      </c>
-      <c r="H11" s="153">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="153" t="s">
+      <c r="A12" t="s">
         <v>209</v>
       </c>
-      <c r="B12" s="153">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="153">
+      <c r="C12">
         <v>1345.5035912673</v>
       </c>
-      <c r="D12" s="153">
+      <c r="D12">
         <v>4925.6892500217</v>
       </c>
-      <c r="E12" s="153">
+      <c r="E12">
         <v>23409635.228719268</v>
       </c>
-      <c r="F12" s="153">
-        <v>0</v>
-      </c>
-      <c r="G12" s="153">
-        <v>0</v>
-      </c>
-      <c r="H12" s="153">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="153" t="s">
+      <c r="A13" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="153">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="153">
+      <c r="C13">
         <v>1560.6165992035001</v>
       </c>
-      <c r="D13" s="153">
+      <c r="D13">
         <v>3529.3291428728999</v>
       </c>
-      <c r="E13" s="153">
+      <c r="E13">
         <v>29335856.927223582</v>
       </c>
-      <c r="F13" s="153">
-        <v>0</v>
-      </c>
-      <c r="G13" s="153">
-        <v>0</v>
-      </c>
-      <c r="H13" s="153">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="153" t="s">
+      <c r="A14" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="153">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="153">
+      <c r="C14">
         <v>6598.3796527765999</v>
       </c>
-      <c r="D14" s="153">
+      <c r="D14">
         <v>32111.143909222501</v>
       </c>
-      <c r="E14" s="153">
+      <c r="E14">
         <v>102087212.84340489</v>
       </c>
-      <c r="F14" s="153">
-        <v>0</v>
-      </c>
-      <c r="G14" s="153">
-        <v>0</v>
-      </c>
-      <c r="H14" s="153">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="153" t="s">
+      <c r="A15" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="153">
+      <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" s="153">
+      <c r="C15">
         <v>1231.2680555543</v>
       </c>
-      <c r="D15" s="153">
+      <c r="D15">
         <v>4225.3905119124001</v>
       </c>
-      <c r="E15" s="153">
+      <c r="E15">
         <v>25390866.545600012</v>
       </c>
-      <c r="F15" s="153">
-        <v>0</v>
-      </c>
-      <c r="G15" s="153">
-        <v>0</v>
-      </c>
-      <c r="H15" s="153">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="153" t="s">
+      <c r="A16" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="153">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="153">
+      <c r="C16">
         <v>804.26751984019995</v>
       </c>
-      <c r="D16" s="153">
+      <c r="D16">
         <v>3167.7384524029999</v>
       </c>
-      <c r="E16" s="153">
+      <c r="E16">
         <v>20496296.761593435</v>
       </c>
-      <c r="F16" s="153">
-        <v>0</v>
-      </c>
-      <c r="G16" s="153">
-        <v>0</v>
-      </c>
-      <c r="H16" s="153">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="153" t="s">
+      <c r="A17" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="153">
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="153">
+      <c r="C17">
         <v>1714.6691071415</v>
       </c>
-      <c r="D17" s="153">
+      <c r="D17">
         <v>5481.9802262014</v>
       </c>
-      <c r="E17" s="153">
+      <c r="E17">
         <v>37706154.815905802</v>
       </c>
-      <c r="F17" s="153">
-        <v>0</v>
-      </c>
-      <c r="G17" s="153">
-        <v>0</v>
-      </c>
-      <c r="H17" s="153">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="153" t="s">
+      <c r="A18" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="153">
+      <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="153">
+      <c r="C18">
         <v>1960.4660515854</v>
       </c>
-      <c r="D18" s="153">
+      <c r="D18">
         <v>8902.3901785972994</v>
       </c>
-      <c r="E18" s="153">
+      <c r="E18">
         <v>41610406.274805903</v>
       </c>
-      <c r="F18" s="153">
-        <v>0</v>
-      </c>
-      <c r="G18" s="153">
-        <v>0</v>
-      </c>
-      <c r="H18" s="153">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="153" t="s">
+      <c r="A19" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="153">
+      <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="153">
+      <c r="C19">
         <v>1616.7055158699</v>
       </c>
-      <c r="D19" s="153">
+      <c r="D19">
         <v>6291.3133333428004</v>
       </c>
-      <c r="E19" s="153">
+      <c r="E19">
         <v>34465432.612347864</v>
       </c>
-      <c r="F19" s="153">
-        <v>0</v>
-      </c>
-      <c r="G19" s="153">
-        <v>0</v>
-      </c>
-      <c r="H19" s="153">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="153" t="s">
+      <c r="A20" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="153">
+      <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="153">
+      <c r="C20">
         <v>5247.8461805548004</v>
       </c>
-      <c r="D20" s="153">
+      <c r="D20">
         <v>30126.3908377886</v>
       </c>
-      <c r="E20" s="153">
+      <c r="E20">
         <v>96700883.205506235</v>
       </c>
-      <c r="F20" s="153">
-        <v>0</v>
-      </c>
-      <c r="G20" s="153">
-        <v>0</v>
-      </c>
-      <c r="H20" s="153">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="153" t="s">
+      <c r="A21" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="153">
+      <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="153">
+      <c r="C21">
         <v>627.04738094929996</v>
       </c>
-      <c r="D21" s="153">
+      <c r="D21">
         <v>2317.5228690753002</v>
       </c>
-      <c r="E21" s="153">
+      <c r="E21">
         <v>15149311.124528823</v>
       </c>
-      <c r="F21" s="153">
-        <v>0</v>
-      </c>
-      <c r="G21" s="153">
-        <v>0</v>
-      </c>
-      <c r="H21" s="153">
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="153" t="s">
+      <c r="A22" t="s">
         <v>276</v>
       </c>
-      <c r="B22" s="153">
+      <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" s="153">
+      <c r="C22">
         <v>431.37722883560002</v>
       </c>
-      <c r="D22" s="153">
+      <c r="D22">
         <v>1752.2244166864</v>
       </c>
-      <c r="E22" s="153">
+      <c r="E22">
         <v>9113051.1413762029</v>
       </c>
-      <c r="F22" s="153">
-        <v>0</v>
-      </c>
-      <c r="G22" s="153">
-        <v>0</v>
-      </c>
-      <c r="H22" s="153">
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="153" t="s">
+      <c r="A23" t="s">
         <v>267</v>
       </c>
-      <c r="B23" s="153">
+      <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" s="153">
+      <c r="C23">
         <v>4622.7102777765003</v>
       </c>
-      <c r="D23" s="153">
+      <c r="D23">
         <v>25037.299678570402</v>
       </c>
-      <c r="E23" s="153">
+      <c r="E23">
         <v>81717971.005489424</v>
       </c>
-      <c r="F23" s="153">
-        <v>0</v>
-      </c>
-      <c r="G23" s="153">
-        <v>0</v>
-      </c>
-      <c r="H23" s="153">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="153" t="s">
+      <c r="A24" t="s">
         <v>266</v>
       </c>
-      <c r="B24" s="153">
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" s="153">
+      <c r="C24">
         <v>3104.2488095231001</v>
       </c>
-      <c r="D24" s="153">
+      <c r="D24">
         <v>28021.333214282</v>
       </c>
-      <c r="E24" s="153">
+      <c r="E24">
         <v>55057645.412610985</v>
       </c>
-      <c r="F24" s="153">
-        <v>0</v>
-      </c>
-      <c r="G24" s="153">
-        <v>0</v>
-      </c>
-      <c r="H24" s="153">
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="153" t="s">
+      <c r="A25" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="153">
+      <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" s="153">
+      <c r="C25">
         <v>913.39481348979996</v>
       </c>
-      <c r="D25" s="153">
+      <c r="D25">
         <v>4213.0360952469</v>
       </c>
-      <c r="E25" s="153">
+      <c r="E25">
         <v>21391786.042081032</v>
       </c>
-      <c r="F25" s="153">
-        <v>0</v>
-      </c>
-      <c r="G25" s="153">
-        <v>0</v>
-      </c>
-      <c r="H25" s="153">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="153" t="s">
+      <c r="A26" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="153">
+      <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26" s="153">
+      <c r="C26">
         <v>852.03371031280005</v>
       </c>
-      <c r="D26" s="153">
+      <c r="D26">
         <v>2459.5965475989001</v>
       </c>
-      <c r="E26" s="153">
+      <c r="E26">
         <v>14568130.544950163</v>
       </c>
-      <c r="F26" s="153">
-        <v>0</v>
-      </c>
-      <c r="G26" s="153">
-        <v>0</v>
-      </c>
-      <c r="H26" s="153">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="153" t="s">
+      <c r="A27" t="s">
         <v>217</v>
       </c>
-      <c r="B27" s="153">
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" s="153">
+      <c r="C27">
         <v>8391.2722222224002</v>
       </c>
-      <c r="D27" s="153">
+      <c r="D27">
         <v>28013.4</v>
       </c>
-      <c r="E27" s="153">
+      <c r="E27">
         <v>101824057.65645294</v>
       </c>
-      <c r="F27" s="153">
-        <v>0</v>
-      </c>
-      <c r="G27" s="153">
-        <v>0</v>
-      </c>
-      <c r="H27" s="153">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="153" t="s">
+      <c r="A28" t="s">
         <v>219</v>
       </c>
-      <c r="B28" s="153">
+      <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="153">
+      <c r="C28">
         <v>1275.0220634866</v>
       </c>
-      <c r="D28" s="153">
+      <c r="D28">
         <v>5048.5304642831998</v>
       </c>
-      <c r="E28" s="153">
+      <c r="E28">
         <v>25572672.63372704</v>
       </c>
-      <c r="F28" s="153">
-        <v>0</v>
-      </c>
-      <c r="G28" s="153">
-        <v>0</v>
-      </c>
-      <c r="H28" s="153">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="153" t="s">
+      <c r="A29" t="s">
         <v>211</v>
       </c>
-      <c r="B29" s="153">
+      <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29" s="153">
+      <c r="C29">
         <v>3353.4049603161998</v>
       </c>
-      <c r="D29" s="153">
+      <c r="D29">
         <v>16559.3793333346</v>
       </c>
-      <c r="E29" s="153">
+      <c r="E29">
         <v>57829766.086974263</v>
       </c>
-      <c r="F29" s="153">
-        <v>0</v>
-      </c>
-      <c r="G29" s="153">
-        <v>0</v>
-      </c>
-      <c r="H29" s="153">
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="153" t="s">
+      <c r="A30" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="153">
+      <c r="B30">
         <v>1</v>
       </c>
-      <c r="C30" s="153">
+      <c r="C30">
         <v>457.67793650610002</v>
       </c>
-      <c r="D30" s="153">
+      <c r="D30">
         <v>1497.9925952345</v>
       </c>
-      <c r="E30" s="153">
+      <c r="E30">
         <v>9735931.1299433764</v>
       </c>
-      <c r="F30" s="153">
-        <v>0</v>
-      </c>
-      <c r="G30" s="153">
-        <v>0</v>
-      </c>
-      <c r="H30" s="153">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="153" t="s">
+      <c r="A31" t="s">
         <v>213</v>
       </c>
-      <c r="B31" s="153">
+      <c r="B31">
         <v>1</v>
       </c>
-      <c r="C31" s="153">
+      <c r="C31">
         <v>800.18710317340003</v>
       </c>
-      <c r="D31" s="153">
+      <c r="D31">
         <v>2217.2120833448998</v>
       </c>
-      <c r="E31" s="153">
+      <c r="E31">
         <v>11963691.606818626</v>
       </c>
-      <c r="F31" s="153">
-        <v>0</v>
-      </c>
-      <c r="G31" s="153">
-        <v>0</v>
-      </c>
-      <c r="H31" s="153">
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="153" t="s">
+      <c r="A32" t="s">
         <v>274</v>
       </c>
-      <c r="B32" s="153">
+      <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32" s="153">
+      <c r="C32">
         <v>158.864742062</v>
       </c>
-      <c r="D32" s="153">
+      <c r="D32">
         <v>757.51541666109995</v>
       </c>
-      <c r="E32" s="153">
+      <c r="E32">
         <v>5709713.1251462931</v>
       </c>
-      <c r="F32" s="153">
-        <v>0</v>
-      </c>
-      <c r="G32" s="153">
-        <v>0</v>
-      </c>
-      <c r="H32" s="153">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="153" t="s">
+      <c r="A33" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="153">
+      <c r="B33">
         <v>1</v>
       </c>
-      <c r="C33" s="153">
+      <c r="C33">
         <v>1250.0606944429001</v>
       </c>
-      <c r="D33" s="153">
+      <c r="D33">
         <v>5122.8165833367002</v>
       </c>
-      <c r="E33" s="153">
+      <c r="E33">
         <v>19785141.165386483</v>
       </c>
-      <c r="F33" s="153">
-        <v>0</v>
-      </c>
-      <c r="G33" s="153">
-        <v>0</v>
-      </c>
-      <c r="H33" s="153">
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="153" t="s">
+      <c r="A34" t="s">
         <v>270</v>
       </c>
-      <c r="B34" s="153">
+      <c r="B34">
         <v>1</v>
       </c>
-      <c r="C34" s="153">
+      <c r="C34">
         <v>163.21921335210001</v>
       </c>
-      <c r="D34" s="153">
+      <c r="D34">
         <v>1932.7814166661001</v>
       </c>
-      <c r="E34" s="153">
+      <c r="E34">
         <v>5241126.1151039721</v>
       </c>
-      <c r="F34" s="153">
-        <v>0</v>
-      </c>
-      <c r="G34" s="153">
-        <v>0</v>
-      </c>
-      <c r="H34" s="153">
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="153" t="s">
+      <c r="A35" t="s">
         <v>268</v>
       </c>
-      <c r="B35" s="153">
+      <c r="B35">
         <v>1</v>
       </c>
-      <c r="C35" s="153">
+      <c r="C35">
         <v>1827.5875000000001</v>
       </c>
-      <c r="D35" s="153">
+      <c r="D35">
         <v>11987.440000000201</v>
       </c>
-      <c r="E35" s="153">
+      <c r="E35">
         <v>24185979.343219414</v>
       </c>
-      <c r="F35" s="153">
-        <v>0</v>
-      </c>
-      <c r="G35" s="153">
-        <v>0</v>
-      </c>
-      <c r="H35" s="153">
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="153" t="s">
+      <c r="A36" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="153">
+      <c r="B36">
         <v>1</v>
       </c>
-      <c r="C36" s="153">
+      <c r="C36">
         <v>945.45267857040005</v>
       </c>
-      <c r="D36" s="153">
+      <c r="D36">
         <v>4044.1207321779002</v>
       </c>
-      <c r="E36" s="153">
+      <c r="E36">
         <v>22290249.207253531</v>
       </c>
-      <c r="F36" s="153">
-        <v>0</v>
-      </c>
-      <c r="G36" s="153">
-        <v>0</v>
-      </c>
-      <c r="H36" s="153">
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="153" t="s">
+      <c r="A37" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="153">
+      <c r="B37">
         <v>1</v>
       </c>
-      <c r="C37" s="153">
+      <c r="C37">
         <v>922.34910714299997</v>
       </c>
-      <c r="D37" s="153">
+      <c r="D37">
         <v>5556.3775000114001</v>
       </c>
-      <c r="E37" s="153">
+      <c r="E37">
         <v>19388227.995180633</v>
       </c>
-      <c r="F37" s="153">
-        <v>0</v>
-      </c>
-      <c r="G37" s="153">
-        <v>0</v>
-      </c>
-      <c r="H37" s="153">
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="153" t="s">
+      <c r="A38" t="s">
         <v>272</v>
       </c>
-      <c r="B38" s="153">
+      <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38" s="153">
+      <c r="C38">
         <v>1472</v>
       </c>
-      <c r="D38" s="153">
+      <c r="D38">
         <v>14874.379999997</v>
       </c>
-      <c r="E38" s="153">
+      <c r="E38">
         <v>34302310.373550735</v>
       </c>
-      <c r="F38" s="153">
-        <v>0</v>
-      </c>
-      <c r="G38" s="153">
-        <v>0</v>
-      </c>
-      <c r="H38" s="153">
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="153" t="s">
+      <c r="A39" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="153">
+      <c r="B39">
         <v>1</v>
       </c>
-      <c r="C39" s="153">
+      <c r="C39">
         <v>1377.3771103895999</v>
       </c>
-      <c r="D39" s="153">
+      <c r="D39">
         <v>16480.505000001402</v>
       </c>
-      <c r="E39" s="153">
+      <c r="E39">
         <v>32498645.480668604</v>
       </c>
-      <c r="F39" s="153">
-        <v>0</v>
-      </c>
-      <c r="G39" s="153">
-        <v>0</v>
-      </c>
-      <c r="H39" s="153">
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="153" t="s">
+      <c r="A40" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="153">
+      <c r="B40">
         <v>1</v>
       </c>
-      <c r="C40" s="153">
+      <c r="C40">
         <v>2355.5015513121998</v>
       </c>
-      <c r="D40" s="153">
+      <c r="D40">
         <v>12552.1444241309</v>
       </c>
-      <c r="E40" s="153">
+      <c r="E40">
         <v>37352638.429863513</v>
       </c>
-      <c r="F40" s="153">
-        <v>0</v>
-      </c>
-      <c r="G40" s="153">
-        <v>0</v>
-      </c>
-      <c r="H40" s="153">
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="153" t="s">
+      <c r="A41" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="153">
+      <c r="B41">
         <v>1</v>
       </c>
-      <c r="C41" s="153">
+      <c r="C41">
         <v>5239.0556547626002</v>
       </c>
-      <c r="D41" s="153">
+      <c r="D41">
         <v>32322.769416663901</v>
       </c>
-      <c r="E41" s="153">
+      <c r="E41">
         <v>59139346.928738102</v>
       </c>
-      <c r="F41" s="153">
-        <v>0</v>
-      </c>
-      <c r="G41" s="153">
-        <v>0</v>
-      </c>
-      <c r="H41" s="153">
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="153" t="s">
+      <c r="A42" t="s">
         <v>214</v>
       </c>
-      <c r="B42" s="153">
+      <c r="B42">
         <v>1</v>
       </c>
-      <c r="C42" s="153">
+      <c r="C42">
         <v>707.19444444440001</v>
       </c>
-      <c r="D42" s="153">
+      <c r="D42">
         <v>6412.8199999994004</v>
       </c>
-      <c r="E42" s="153">
+      <c r="E42">
         <v>14367535.716373395</v>
       </c>
-      <c r="F42" s="153">
-        <v>0</v>
-      </c>
-      <c r="G42" s="153">
-        <v>0</v>
-      </c>
-      <c r="H42" s="153">
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="153" t="s">
+      <c r="A43" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="153">
+      <c r="B43">
         <v>1</v>
       </c>
-      <c r="C43" s="153">
+      <c r="C43">
         <v>572.94241071370004</v>
       </c>
-      <c r="D43" s="153">
+      <c r="D43">
         <v>2383.8024318439002</v>
       </c>
-      <c r="E43" s="153">
+      <c r="E43">
         <v>23761816.928639762</v>
       </c>
-      <c r="F43" s="153">
-        <v>0</v>
-      </c>
-      <c r="G43" s="153">
-        <v>0</v>
-      </c>
-      <c r="H43" s="153">
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="153" t="s">
+      <c r="A44" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="153">
+      <c r="B44">
         <v>1</v>
       </c>
-      <c r="C44" s="153">
+      <c r="C44">
         <v>668.72827381019999</v>
       </c>
-      <c r="D44" s="153">
+      <c r="D44">
         <v>3906.8632381042999</v>
       </c>
-      <c r="E44" s="153">
+      <c r="E44">
         <v>12804899.463654276</v>
       </c>
-      <c r="F44" s="153">
-        <v>0</v>
-      </c>
-      <c r="G44" s="153">
-        <v>0</v>
-      </c>
-      <c r="H44" s="153">
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="153" t="s">
+      <c r="A45" t="s">
         <v>275</v>
       </c>
-      <c r="B45" s="153">
+      <c r="B45">
         <v>1</v>
       </c>
-      <c r="C45" s="153">
+      <c r="C45">
         <v>402.446428572</v>
       </c>
-      <c r="D45" s="153">
+      <c r="D45">
         <v>479.95833333079997</v>
       </c>
-      <c r="E45" s="153">
+      <c r="E45">
         <v>7202966.5073920414</v>
       </c>
-      <c r="F45" s="153">
-        <v>0</v>
-      </c>
-      <c r="G45" s="153">
-        <v>0</v>
-      </c>
-      <c r="H45" s="153">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="153" t="s">
+      <c r="A46" t="s">
         <v>154</v>
       </c>
-      <c r="B46" s="153">
+      <c r="B46">
         <v>1</v>
       </c>
-      <c r="C46" s="153">
+      <c r="C46">
         <v>1167.4939583324001</v>
       </c>
-      <c r="D46" s="153">
+      <c r="D46">
         <v>2726.4949568356001</v>
       </c>
-      <c r="E46" s="153">
+      <c r="E46">
         <v>13798283.853042893</v>
       </c>
-      <c r="F46" s="153">
-        <v>0</v>
-      </c>
-      <c r="G46" s="153">
-        <v>0</v>
-      </c>
-      <c r="H46" s="153">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="153" t="s">
+      <c r="A47" t="s">
         <v>218</v>
       </c>
-      <c r="B47" s="153">
+      <c r="B47">
         <v>1</v>
       </c>
-      <c r="C47" s="153">
+      <c r="C47">
         <v>1422.5815873009001</v>
       </c>
-      <c r="D47" s="153">
+      <c r="D47">
         <v>7672.6542023802003</v>
       </c>
-      <c r="E47" s="153">
+      <c r="E47">
         <v>22591494.174129337</v>
       </c>
-      <c r="F47" s="153">
-        <v>0</v>
-      </c>
-      <c r="G47" s="153">
-        <v>0</v>
-      </c>
-      <c r="H47" s="153">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -9371,7 +9370,7 @@
       <c r="L2" s="105">
         <v>907871.92636018235</v>
       </c>
-      <c r="N2" s="151" t="s">
+      <c r="N2" s="152" t="s">
         <v>37</v>
       </c>
       <c r="O2">
@@ -9434,7 +9433,7 @@
       <c r="L3" s="107">
         <v>707919.37019508681</v>
       </c>
-      <c r="N3" s="151"/>
+      <c r="N3" s="152"/>
       <c r="O3">
         <v>49</v>
       </c>
@@ -9495,7 +9494,7 @@
       <c r="L4" s="107">
         <v>276942.08389738784</v>
       </c>
-      <c r="N4" s="151"/>
+      <c r="N4" s="152"/>
       <c r="O4">
         <v>20</v>
       </c>
@@ -9556,7 +9555,7 @@
       <c r="L5" s="107">
         <v>699165.05217344186</v>
       </c>
-      <c r="N5" s="151"/>
+      <c r="N5" s="152"/>
       <c r="O5">
         <v>15</v>
       </c>
@@ -9617,7 +9616,7 @@
       <c r="L6" s="107">
         <v>0</v>
       </c>
-      <c r="N6" s="151"/>
+      <c r="N6" s="152"/>
       <c r="O6">
         <v>19</v>
       </c>
@@ -9678,7 +9677,7 @@
       <c r="L7" s="107">
         <v>265320.43464193383</v>
       </c>
-      <c r="N7" s="151"/>
+      <c r="N7" s="152"/>
       <c r="O7">
         <v>16</v>
       </c>
@@ -9739,7 +9738,7 @@
       <c r="L8" s="107">
         <v>454186.93616588484</v>
       </c>
-      <c r="N8" s="151"/>
+      <c r="N8" s="152"/>
       <c r="O8">
         <v>12</v>
       </c>
@@ -9800,7 +9799,7 @@
       <c r="L9" s="107">
         <v>801417.68719647545</v>
       </c>
-      <c r="N9" s="151"/>
+      <c r="N9" s="152"/>
       <c r="O9">
         <v>11</v>
       </c>
@@ -9857,7 +9856,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="112"/>
-      <c r="N10" s="151"/>
+      <c r="N10" s="152"/>
       <c r="O10">
         <v>8</v>
       </c>
@@ -9920,7 +9919,7 @@
       <c r="L11" s="105">
         <v>473999.33273359912</v>
       </c>
-      <c r="N11" s="151"/>
+      <c r="N11" s="152"/>
       <c r="O11">
         <v>52</v>
       </c>
@@ -9981,7 +9980,7 @@
       <c r="L12" s="107">
         <v>0</v>
       </c>
-      <c r="N12" s="151"/>
+      <c r="N12" s="152"/>
       <c r="O12">
         <v>53</v>
       </c>
@@ -10042,7 +10041,7 @@
       <c r="L13" s="107">
         <v>1774250.1300302623</v>
       </c>
-      <c r="N13" s="151"/>
+      <c r="N13" s="152"/>
       <c r="O13">
         <v>5</v>
       </c>
@@ -10103,7 +10102,7 @@
       <c r="L14" s="107">
         <v>688681.10694474855</v>
       </c>
-      <c r="N14" s="151"/>
+      <c r="N14" s="152"/>
       <c r="O14">
         <v>4</v>
       </c>
@@ -10164,7 +10163,7 @@
       <c r="L15" s="107">
         <v>542644.60453174426</v>
       </c>
-      <c r="N15" s="152"/>
+      <c r="N15" s="153"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="14"/>
@@ -10210,7 +10209,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L16" s="112"/>
-      <c r="N16" s="150" t="s">
+      <c r="N16" s="151" t="s">
         <v>38</v>
       </c>
       <c r="O16">
@@ -10275,7 +10274,7 @@
       <c r="L17" s="105">
         <v>0</v>
       </c>
-      <c r="N17" s="151"/>
+      <c r="N17" s="152"/>
       <c r="O17">
         <v>54</v>
       </c>
@@ -10336,7 +10335,7 @@
       <c r="L18" s="107">
         <v>0</v>
       </c>
-      <c r="N18" s="151"/>
+      <c r="N18" s="152"/>
       <c r="O18">
         <v>21</v>
       </c>
@@ -10397,7 +10396,7 @@
       <c r="L19" s="107">
         <v>0</v>
       </c>
-      <c r="N19" s="151"/>
+      <c r="N19" s="152"/>
       <c r="O19">
         <v>23</v>
       </c>
@@ -10458,7 +10457,7 @@
       <c r="L20" s="107">
         <v>532961.24250140926</v>
       </c>
-      <c r="N20" s="151"/>
+      <c r="N20" s="152"/>
       <c r="O20">
         <v>18</v>
       </c>
@@ -10519,7 +10518,7 @@
       <c r="L21" s="107">
         <v>243114.33850570052</v>
       </c>
-      <c r="N21" s="151"/>
+      <c r="N21" s="152"/>
       <c r="O21">
         <v>44</v>
       </c>
@@ -10580,7 +10579,7 @@
       <c r="L22" s="107">
         <v>399885.11500273226</v>
       </c>
-      <c r="N22" s="151"/>
+      <c r="N22" s="152"/>
       <c r="O22">
         <v>56</v>
       </c>
@@ -10641,7 +10640,7 @@
       <c r="L23" s="107">
         <v>0</v>
       </c>
-      <c r="N23" s="151"/>
+      <c r="N23" s="152"/>
       <c r="O23">
         <v>2</v>
       </c>
@@ -10702,7 +10701,7 @@
       <c r="L24" s="107">
         <v>532480.47978304385</v>
       </c>
-      <c r="N24" s="151"/>
+      <c r="N24" s="152"/>
       <c r="O24">
         <v>3</v>
       </c>
@@ -10763,7 +10762,7 @@
       <c r="L25" s="107">
         <v>855398.40214226511</v>
       </c>
-      <c r="N25" s="152"/>
+      <c r="N25" s="153"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="23"/>
       <c r="R25" s="14"/>
@@ -10809,7 +10808,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L26" s="112"/>
-      <c r="N26" s="150" t="s">
+      <c r="N26" s="151" t="s">
         <v>222</v>
       </c>
       <c r="O26">
@@ -10874,7 +10873,7 @@
       <c r="L27" s="105">
         <v>0</v>
       </c>
-      <c r="N27" s="151"/>
+      <c r="N27" s="152"/>
       <c r="O27">
         <v>36</v>
       </c>
@@ -10935,7 +10934,7 @@
       <c r="L28" s="107">
         <v>0</v>
       </c>
-      <c r="N28" s="151"/>
+      <c r="N28" s="152"/>
       <c r="O28">
         <v>9</v>
       </c>
@@ -10996,7 +10995,7 @@
       <c r="L29" s="107">
         <v>0</v>
       </c>
-      <c r="N29" s="151"/>
+      <c r="N29" s="152"/>
       <c r="O29">
         <v>40</v>
       </c>
@@ -11057,7 +11056,7 @@
       <c r="L30" s="107">
         <v>0</v>
       </c>
-      <c r="N30" s="151"/>
+      <c r="N30" s="152"/>
       <c r="O30">
         <v>27</v>
       </c>
@@ -11118,7 +11117,7 @@
       <c r="L31" s="107">
         <v>245173.74682820804</v>
       </c>
-      <c r="N31" s="151"/>
+      <c r="N31" s="152"/>
       <c r="O31">
         <v>10</v>
       </c>
@@ -11179,7 +11178,7 @@
       <c r="L32" s="107">
         <v>0</v>
       </c>
-      <c r="N32" s="151"/>
+      <c r="N32" s="152"/>
       <c r="O32">
         <v>28</v>
       </c>
@@ -11240,7 +11239,7 @@
       <c r="L33" s="107">
         <v>0</v>
       </c>
-      <c r="N33" s="151"/>
+      <c r="N33" s="152"/>
       <c r="O33">
         <v>33</v>
       </c>
@@ -11301,7 +11300,7 @@
       <c r="L34" s="107">
         <v>0</v>
       </c>
-      <c r="N34" s="151"/>
+      <c r="N34" s="152"/>
       <c r="O34">
         <v>37</v>
       </c>
@@ -11362,7 +11361,7 @@
       <c r="L35" s="107">
         <v>0</v>
       </c>
-      <c r="N35" s="151"/>
+      <c r="N35" s="152"/>
       <c r="O35">
         <v>24</v>
       </c>
@@ -11423,7 +11422,7 @@
       <c r="L36" s="107">
         <v>0</v>
       </c>
-      <c r="N36" s="151"/>
+      <c r="N36" s="152"/>
       <c r="O36">
         <v>7</v>
       </c>
@@ -11484,7 +11483,7 @@
       <c r="L37" s="107">
         <v>0</v>
       </c>
-      <c r="N37" s="151"/>
+      <c r="N37" s="152"/>
       <c r="O37">
         <v>57</v>
       </c>
@@ -11545,7 +11544,7 @@
       <c r="L38" s="107">
         <v>0</v>
       </c>
-      <c r="N38" s="151"/>
+      <c r="N38" s="152"/>
       <c r="O38">
         <v>1</v>
       </c>
@@ -11606,7 +11605,7 @@
       <c r="L39" s="107">
         <v>0</v>
       </c>
-      <c r="N39" s="152"/>
+      <c r="N39" s="153"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="23"/>
       <c r="R39" s="14"/>
@@ -13656,7 +13655,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="145" t="s">
         <v>206</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -13708,7 +13707,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="145"/>
+      <c r="A3" s="146"/>
       <c r="B3" s="36" t="s">
         <v>93</v>
       </c>
@@ -13759,7 +13758,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="145"/>
+      <c r="A4" s="146"/>
       <c r="B4" s="36" t="s">
         <v>91</v>
       </c>
@@ -13809,7 +13808,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="145"/>
+      <c r="A5" s="146"/>
       <c r="B5" s="36" t="s">
         <v>89</v>
       </c>
@@ -13853,7 +13852,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="145"/>
+      <c r="A6" s="146"/>
       <c r="B6" s="36" t="s">
         <v>209</v>
       </c>
@@ -13897,7 +13896,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="145"/>
+      <c r="A7" s="146"/>
       <c r="B7" s="36" t="s">
         <v>271</v>
       </c>
@@ -13941,7 +13940,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="145"/>
+      <c r="A8" s="146"/>
       <c r="B8" s="36" t="s">
         <v>84</v>
       </c>
@@ -13985,7 +13984,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="145"/>
+      <c r="A9" s="146"/>
       <c r="B9" s="36" t="s">
         <v>83</v>
       </c>
@@ -14029,7 +14028,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="146"/>
+      <c r="A10" s="147"/>
       <c r="B10" s="3"/>
       <c r="C10" s="64">
         <v>242974591.73925051</v>
@@ -14068,7 +14067,7 @@
       <c r="L10" s="68"/>
     </row>
     <row r="11" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="144" t="s">
+      <c r="A11" s="145" t="s">
         <v>207</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -14114,7 +14113,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="145"/>
+      <c r="A12" s="146"/>
       <c r="B12" s="36" t="s">
         <v>90</v>
       </c>
@@ -14164,7 +14163,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="145"/>
+      <c r="A13" s="146"/>
       <c r="B13" s="36" t="s">
         <v>272</v>
       </c>
@@ -14209,7 +14208,7 @@
       <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="145"/>
+      <c r="A14" s="146"/>
       <c r="B14" s="36" t="s">
         <v>107</v>
       </c>
@@ -14253,7 +14252,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="146"/>
+      <c r="A15" s="147"/>
       <c r="B15" s="3"/>
       <c r="C15" s="64">
         <v>341864881.75327951</v>
@@ -14292,7 +14291,7 @@
       <c r="L15" s="68"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="147" t="s">
+      <c r="A16" s="148" t="s">
         <v>208</v>
       </c>
       <c r="B16" s="69" t="s">
@@ -14338,7 +14337,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="148"/>
+      <c r="A17" s="149"/>
       <c r="B17" s="19" t="s">
         <v>82</v>
       </c>
@@ -14382,7 +14381,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="148"/>
+      <c r="A18" s="149"/>
       <c r="B18" s="19" t="s">
         <v>92</v>
       </c>
@@ -14426,7 +14425,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="148"/>
+      <c r="A19" s="149"/>
       <c r="B19" s="19" t="s">
         <v>95</v>
       </c>
@@ -14470,7 +14469,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="148"/>
+      <c r="A20" s="149"/>
       <c r="B20" s="19" t="s">
         <v>97</v>
       </c>
@@ -14514,7 +14513,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="148"/>
+      <c r="A21" s="149"/>
       <c r="B21" s="19" t="s">
         <v>219</v>
       </c>
@@ -14558,7 +14557,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="148"/>
+      <c r="A22" s="149"/>
       <c r="B22" s="19" t="s">
         <v>160</v>
       </c>
@@ -14602,7 +14601,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="148"/>
+      <c r="A23" s="149"/>
       <c r="B23" s="19" t="s">
         <v>220</v>
       </c>
@@ -14646,7 +14645,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="149"/>
+      <c r="A24" s="150"/>
       <c r="B24" s="72"/>
       <c r="C24" s="67">
         <v>237630000</v>
@@ -14685,7 +14684,7 @@
       <c r="L24" s="68"/>
     </row>
     <row r="25" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="144" t="s">
+      <c r="A25" s="145" t="s">
         <v>216</v>
       </c>
       <c r="B25" s="57" t="s">
@@ -14731,7 +14730,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="145"/>
+      <c r="A26" s="146"/>
       <c r="B26" s="36" t="s">
         <v>213</v>
       </c>
@@ -14775,7 +14774,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="145"/>
+      <c r="A27" s="146"/>
       <c r="B27" s="36" t="s">
         <v>86</v>
       </c>
@@ -14820,7 +14819,7 @@
       <c r="M27" s="27"/>
     </row>
     <row r="28" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="145"/>
+      <c r="A28" s="146"/>
       <c r="B28" s="36" t="s">
         <v>212</v>
       </c>
@@ -14865,7 +14864,7 @@
       <c r="M28" s="26"/>
     </row>
     <row r="29" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="145"/>
+      <c r="A29" s="146"/>
       <c r="B29" s="36" t="s">
         <v>98</v>
       </c>
@@ -14910,7 +14909,7 @@
       <c r="M29" s="27"/>
     </row>
     <row r="30" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="145"/>
+      <c r="A30" s="146"/>
       <c r="B30" s="36" t="s">
         <v>210</v>
       </c>
@@ -14955,7 +14954,7 @@
       <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="145"/>
+      <c r="A31" s="146"/>
       <c r="B31" s="36" t="s">
         <v>99</v>
       </c>
@@ -14999,7 +14998,7 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="145"/>
+      <c r="A32" s="146"/>
       <c r="B32" s="36" t="s">
         <v>138</v>
       </c>
@@ -15043,7 +15042,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="145"/>
+      <c r="A33" s="146"/>
       <c r="B33" s="19" t="s">
         <v>274</v>
       </c>
@@ -15087,7 +15086,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="145"/>
+      <c r="A34" s="146"/>
       <c r="B34" s="36" t="s">
         <v>276</v>
       </c>
@@ -15131,7 +15130,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="145"/>
+      <c r="A35" s="146"/>
       <c r="B35" s="36" t="s">
         <v>110</v>
       </c>
@@ -15175,7 +15174,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="145"/>
+      <c r="A36" s="146"/>
       <c r="B36" s="36" t="s">
         <v>214</v>
       </c>
@@ -15219,7 +15218,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="145"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="36" t="s">
         <v>80</v>
       </c>
@@ -15263,7 +15262,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="146"/>
+      <c r="A38" s="147"/>
       <c r="B38" s="3"/>
       <c r="C38" s="75">
         <v>521754707.42240375</v>
@@ -15302,7 +15301,7 @@
       <c r="L38" s="68"/>
     </row>
     <row r="39" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="144" t="s">
+      <c r="A39" s="145" t="s">
         <v>265</v>
       </c>
       <c r="B39" s="138" t="s">
@@ -15348,7 +15347,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="145"/>
+      <c r="A40" s="146"/>
       <c r="B40" s="138" t="s">
         <v>145</v>
       </c>
@@ -15392,7 +15391,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="145"/>
+      <c r="A41" s="146"/>
       <c r="B41" s="138" t="s">
         <v>106</v>
       </c>
@@ -15436,7 +15435,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="145"/>
+      <c r="A42" s="146"/>
       <c r="B42" s="139" t="s">
         <v>139</v>
       </c>
@@ -15480,7 +15479,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="145"/>
+      <c r="A43" s="146"/>
       <c r="B43" s="140" t="s">
         <v>266</v>
       </c>
@@ -15524,7 +15523,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="145"/>
+      <c r="A44" s="146"/>
       <c r="B44" s="140" t="s">
         <v>267</v>
       </c>
@@ -15568,7 +15567,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="145"/>
+      <c r="A45" s="146"/>
       <c r="B45" s="140" t="s">
         <v>275</v>
       </c>
@@ -15612,7 +15611,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="145"/>
+      <c r="A46" s="146"/>
       <c r="B46" s="140" t="s">
         <v>268</v>
       </c>
@@ -15656,7 +15655,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="146"/>
+      <c r="A47" s="147"/>
       <c r="B47" s="137"/>
       <c r="C47" s="67">
         <v>455695855.27356702</v>
@@ -16544,7 +16543,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="150" t="s">
+      <c r="A15" s="151" t="s">
         <v>38</v>
       </c>
       <c r="B15">
@@ -16585,7 +16584,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="151"/>
+      <c r="A16" s="152"/>
       <c r="B16">
         <v>54</v>
       </c>
@@ -16624,7 +16623,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="151"/>
+      <c r="A17" s="152"/>
       <c r="B17">
         <v>21</v>
       </c>
@@ -16663,7 +16662,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="151"/>
+      <c r="A18" s="152"/>
       <c r="B18">
         <v>23</v>
       </c>
@@ -16702,7 +16701,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="151"/>
+      <c r="A19" s="152"/>
       <c r="B19">
         <v>18</v>
       </c>
@@ -16741,7 +16740,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="151"/>
+      <c r="A20" s="152"/>
       <c r="B20">
         <v>44</v>
       </c>
@@ -16780,7 +16779,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="151"/>
+      <c r="A21" s="152"/>
       <c r="B21">
         <v>2</v>
       </c>
@@ -16819,7 +16818,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="151"/>
+      <c r="A22" s="152"/>
       <c r="B22">
         <v>3</v>
       </c>
@@ -16858,7 +16857,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="152"/>
+      <c r="A23" s="153"/>
       <c r="C23" s="9"/>
       <c r="D23" s="23"/>
       <c r="E23" s="14"/>
@@ -16877,7 +16876,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="150" t="s">
+      <c r="A24" s="151" t="s">
         <v>215</v>
       </c>
       <c r="B24">
@@ -16918,7 +16917,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="151"/>
+      <c r="A25" s="152"/>
       <c r="B25">
         <v>36</v>
       </c>
@@ -16957,7 +16956,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="151"/>
+      <c r="A26" s="152"/>
       <c r="B26">
         <v>9</v>
       </c>
@@ -16996,7 +16995,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="151"/>
+      <c r="A27" s="152"/>
       <c r="B27">
         <v>40</v>
       </c>
@@ -17035,7 +17034,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="151"/>
+      <c r="A28" s="152"/>
       <c r="B28">
         <v>27</v>
       </c>
@@ -17074,7 +17073,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="151"/>
+      <c r="A29" s="152"/>
       <c r="B29">
         <v>10</v>
       </c>
@@ -17113,7 +17112,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="151"/>
+      <c r="A30" s="152"/>
       <c r="B30">
         <v>28</v>
       </c>
@@ -17152,7 +17151,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="151"/>
+      <c r="A31" s="152"/>
       <c r="B31">
         <v>33</v>
       </c>
@@ -17191,7 +17190,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="151"/>
+      <c r="A32" s="152"/>
       <c r="B32">
         <v>37</v>
       </c>
@@ -17230,7 +17229,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="151"/>
+      <c r="A33" s="152"/>
       <c r="B33">
         <v>24</v>
       </c>
@@ -17269,7 +17268,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="151"/>
+      <c r="A34" s="152"/>
       <c r="B34">
         <v>7</v>
       </c>
@@ -17305,7 +17304,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="151"/>
+      <c r="A35" s="152"/>
       <c r="B35">
         <v>57</v>
       </c>
@@ -17341,7 +17340,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="151"/>
+      <c r="A36" s="152"/>
       <c r="B36">
         <v>1</v>
       </c>
@@ -17380,7 +17379,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="152"/>
+      <c r="A37" s="153"/>
       <c r="C37" s="9"/>
       <c r="D37" s="23"/>
       <c r="E37" s="14"/>
@@ -17399,7 +17398,7 @@
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="151" t="s">
         <v>269</v>
       </c>
       <c r="B38">
@@ -17434,7 +17433,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="151"/>
+      <c r="A39" s="152"/>
       <c r="B39">
         <v>59</v>
       </c>
@@ -17467,7 +17466,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="151"/>
+      <c r="A40" s="152"/>
       <c r="B40">
         <v>49</v>
       </c>
@@ -17500,7 +17499,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="151"/>
+      <c r="A41" s="152"/>
       <c r="B41">
         <v>56</v>
       </c>
@@ -17533,7 +17532,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="151"/>
+      <c r="A42" s="152"/>
       <c r="B42">
         <v>26</v>
       </c>
@@ -17566,7 +17565,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="151"/>
+      <c r="A43" s="152"/>
       <c r="B43">
         <v>25</v>
       </c>
@@ -17599,7 +17598,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="151"/>
+      <c r="A44" s="152"/>
       <c r="B44">
         <v>60</v>
       </c>
@@ -17632,7 +17631,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="151"/>
+      <c r="A45" s="152"/>
       <c r="B45">
         <v>43</v>
       </c>
@@ -27797,7 +27796,7 @@
       </c>
       <c r="C2" s="133"/>
       <c r="D2" s="133">
-        <v>0.16454644097222221</v>
+        <v>0.15894531249999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -27810,7 +27809,7 @@
       </c>
       <c r="C3" s="133"/>
       <c r="D3" s="133">
-        <v>0.26424040316358022</v>
+        <v>0.26660440779320982</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -27823,7 +27822,7 @@
       </c>
       <c r="C4" s="133"/>
       <c r="D4" s="133">
-        <v>0.24291507523148148</v>
+        <v>0.2419609375</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -27836,7 +27835,7 @@
       </c>
       <c r="C5" s="133"/>
       <c r="D5" s="133">
-        <v>0.24158125964506172</v>
+        <v>0.24094540895061728</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -27849,7 +27848,7 @@
       </c>
       <c r="C6" s="133"/>
       <c r="D6" s="133">
-        <v>0.20581602044753083</v>
+        <v>0.20030603780864198</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -27862,7 +27861,7 @@
       </c>
       <c r="C7" s="133"/>
       <c r="D7" s="133">
-        <v>0.23964250578703705</v>
+        <v>0.23877879050925929</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -27875,7 +27874,7 @@
       </c>
       <c r="C8" s="133"/>
       <c r="D8" s="133">
-        <v>0.23243981481481482</v>
+        <v>0.23200506365740742</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -27888,7 +27887,7 @@
       </c>
       <c r="C9" s="133"/>
       <c r="D9" s="133">
-        <v>0.22493851273148149</v>
+        <v>0.22446686921296299</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -27901,7 +27900,7 @@
       </c>
       <c r="C10" s="133"/>
       <c r="D10" s="133">
-        <v>9.2351224922839509E-2</v>
+        <v>9.5327208719135817E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -27914,7 +27913,7 @@
       </c>
       <c r="C11" s="133"/>
       <c r="D11" s="133">
-        <v>0.24307696759259259</v>
+        <v>0.24150000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -27927,7 +27926,7 @@
       </c>
       <c r="C12" s="133"/>
       <c r="D12" s="133">
-        <v>0.27863782793209879</v>
+        <v>0.27755782214506175</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -27940,7 +27939,7 @@
       </c>
       <c r="C13" s="133"/>
       <c r="D13" s="133">
-        <v>0.24616666666666664</v>
+        <v>0.23645891203703698</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -27953,7 +27952,7 @@
       </c>
       <c r="C14" s="133"/>
       <c r="D14" s="133">
-        <v>0.26909442515432103</v>
+        <v>0.26579002700617282</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -27966,7 +27965,7 @@
       </c>
       <c r="C15" s="133"/>
       <c r="D15" s="133">
-        <v>0.22935860339506173</v>
+        <v>0.2264433834876543</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -27979,7 +27978,7 @@
       </c>
       <c r="C16" s="133"/>
       <c r="D16" s="133">
-        <v>0.22326403356481481</v>
+        <v>0.22483666087962961</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -27992,7 +27991,7 @@
       </c>
       <c r="C17" s="133"/>
       <c r="D17" s="133">
-        <v>0.24272453703703703</v>
+        <v>0.24415104166666668</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -28005,7 +28004,7 @@
       </c>
       <c r="C18" s="133"/>
       <c r="D18" s="133">
-        <v>0.24616054205246912</v>
+        <v>0.24397738233024691</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -28018,7 +28017,7 @@
       </c>
       <c r="C19" s="133"/>
       <c r="D19" s="133">
-        <v>0.23944082754629628</v>
+        <v>0.23725766782407409</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -28031,7 +28030,7 @@
       </c>
       <c r="C20" s="133"/>
       <c r="D20" s="133">
-        <v>0.27583810763888889</v>
+        <v>0.28041565393518519</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -28044,7 +28043,7 @@
       </c>
       <c r="C21" s="133"/>
       <c r="D21" s="133">
-        <v>0.22984355709876542</v>
+        <v>0.2298334297839506</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -28057,7 +28056,7 @@
       </c>
       <c r="C22" s="133"/>
       <c r="D22" s="133">
-        <v>0.22385098379629625</v>
+        <v>0.22383579282407406</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -28070,7 +28069,7 @@
       </c>
       <c r="C23" s="133"/>
       <c r="D23" s="133">
-        <v>0.1893315972222222</v>
+        <v>0.1950274884259259</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -28083,7 +28082,7 @@
       </c>
       <c r="C24" s="133"/>
       <c r="D24" s="133">
-        <v>0.24977686149691358</v>
+        <v>0.24920900848765432</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -28096,7 +28095,7 @@
       </c>
       <c r="C25" s="133"/>
       <c r="D25" s="133">
-        <v>0.19736038773148154</v>
+        <v>0.1950795717592593</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -28109,7 +28108,7 @@
       </c>
       <c r="C26" s="133"/>
       <c r="D26" s="133">
-        <v>0.22871624228395063</v>
+        <v>0.2263500675154321</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -28122,7 +28121,7 @@
       </c>
       <c r="C27" s="133"/>
       <c r="D27" s="133">
-        <v>0.23595283564814815</v>
+        <v>0.23228313078703702</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -28135,7 +28134,7 @@
       </c>
       <c r="C28" s="133"/>
       <c r="D28" s="133">
-        <v>0.24907060185185187</v>
+        <v>0.24824594907407405</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -28148,7 +28147,7 @@
       </c>
       <c r="C29" s="133"/>
       <c r="D29" s="133">
-        <v>0.20729817708333334</v>
+        <v>0.21109375</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -28161,7 +28160,7 @@
       </c>
       <c r="C30" s="133"/>
       <c r="D30" s="133">
-        <v>0.19255169753086421</v>
+        <v>0.19017756558641974</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -28174,7 +28173,7 @@
       </c>
       <c r="C31" s="133"/>
       <c r="D31" s="133">
-        <v>0.19816936728395063</v>
+        <v>0.18812813464506173</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -28187,7 +28186,7 @@
       </c>
       <c r="C32" s="133"/>
       <c r="D32" s="133">
-        <v>0.14457961998456786</v>
+        <v>0.16095548804012344</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -28200,7 +28199,7 @@
       </c>
       <c r="C33" s="133"/>
       <c r="D33" s="133">
-        <v>0.19110045331790124</v>
+        <v>0.1868296199845679</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -28226,7 +28225,7 @@
       </c>
       <c r="C35" s="133"/>
       <c r="D35" s="133">
-        <v>0.1251707175925926</v>
+        <v>0.12294777199074075</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -28239,7 +28238,7 @@
       </c>
       <c r="C36" s="133"/>
       <c r="D36" s="133">
-        <v>0.16754372427983535</v>
+        <v>0.16340277777777776</v>
       </c>
     </row>
   </sheetData>
